--- a/eco_conception/composants_ecoinvent.xlsx
+++ b/eco_conception/composants_ecoinvent.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHELELEP\Desktop\GitProj\ProjetElecLORA_GSM\eco_conception\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cd412861\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{22DF296F-0C87-46A9-82A3-FD3F5CDA1C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62653E74-3E95-4B63-9C3E-BEDDAE09B4B6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="composants_ecoinvent" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
   <si>
     <t>Bloc / Carte</t>
   </si>
@@ -245,13 +244,40 @@
   </si>
   <si>
     <t>Cartes</t>
+  </si>
+  <si>
+    <t>Batterie</t>
+  </si>
+  <si>
+    <t>Lithium-ion</t>
+  </si>
+  <si>
+    <t>Boîtier</t>
+  </si>
+  <si>
+    <t>ABS plastic</t>
+  </si>
+  <si>
+    <t>Antennes</t>
+  </si>
+  <si>
+    <t>Énergie</t>
+  </si>
+  <si>
+    <t>kWh/5 ans</t>
+  </si>
+  <si>
+    <t>1,5 à 2 mAh par heure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mAh/h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -779,7 +805,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -787,6 +813,7 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1161,22 +1188,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A673F34E-FE92-45CC-BCA7-98AA30C0CDDE}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.75" customWidth="1"/>
+    <col min="7" max="7" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +1230,7 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1229,7 +1256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1255,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1281,7 +1308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1307,7 +1334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1333,7 +1360,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1359,7 +1386,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1385,7 +1412,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
@@ -1411,7 +1438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
@@ -1437,7 +1464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
@@ -1463,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
@@ -1489,7 +1516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -1515,7 +1542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -1541,7 +1568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1567,7 +1594,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -1593,7 +1620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1619,7 +1646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>47</v>
       </c>
@@ -1645,7 +1672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>47</v>
       </c>
@@ -1671,7 +1698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>47</v>
       </c>
@@ -1697,7 +1724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="5" t="s">
         <v>47</v>
       </c>
@@ -1723,7 +1750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="5" t="s">
         <v>47</v>
       </c>
@@ -1749,7 +1776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="5" t="s">
         <v>47</v>
       </c>
@@ -1775,7 +1802,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="6" t="s">
         <v>73</v>
       </c>
@@ -1801,7 +1828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="6" t="s">
         <v>74</v>
       </c>
@@ -1827,7 +1854,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="6" t="s">
         <v>74</v>
       </c>
@@ -1853,7 +1880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="6" t="s">
         <v>74</v>
       </c>
@@ -1877,6 +1904,81 @@
       </c>
       <c r="H27" s="6" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0.02</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>0.15</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0.03</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>87.6</v>
+      </c>
+      <c r="H32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8">
+      <c r="G33">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="H33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8">
+      <c r="G34" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
